--- a/AAII_Financials/Quarterly/NTR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NTR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>NTR</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10609000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5802000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5142000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5735000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10198000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4874000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4864000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5085000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9916000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5151000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5404000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5368000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11402000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5908000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10233600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11235600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>19629500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10532200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9815500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8132400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>13499300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6203500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5300100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5513700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>10743600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5347400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4492900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5347200</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7358000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4156000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3254000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3771000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7023000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3554000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3283000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3585000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>7004000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3614000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3636000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3741000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8236000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3995000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6285800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6759500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>11511700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6052200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5485200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5209700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9514400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4664000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3731200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4184500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>7978400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4220100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3114200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3885000</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3251000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1646000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1888000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1964000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3175000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1320000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1581000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1500000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2912000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1537000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1768000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1627000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3166000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1913000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3947800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4476100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>8117800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>4480000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4330300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2922800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>3984900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1539600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1569000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1329200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2765200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1127300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1378800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1462200</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,19 +1083,20 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>114000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1090,11 +1104,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>124000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1102,11 +1116,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>114000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,139 +1259,145 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E14" s="3">
         <v>16000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-255000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>52000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>463000</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>176000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>708000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>5000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-432200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-590000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>19300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>37800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>41900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>53900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>30600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-270100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1121800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>67500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>28000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>196200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>53900</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>604000</v>
+      </c>
+      <c r="E15" s="3">
         <v>606000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>140000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>617000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>614000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>571000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>170000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>598000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>586000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>565000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>177000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>552000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>556000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>496000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8757000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5425000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4490000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4962000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8382000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4645000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4442000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4887000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8354000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4740000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4955000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4910000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9549000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5035000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7979800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8208500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12937900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7782600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7347800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6705500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>11260700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5833300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4779300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6455500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>9292200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5243000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4412100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4926500</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1852000</v>
+      </c>
+      <c r="E18" s="3">
         <v>377000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>652000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>773000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1816000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>229000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>422000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>198000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1562000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>411000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>449000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>458000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1853000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>873000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2253800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3027100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6691600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2749600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2467700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1427000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2238600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>370200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>520800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-941800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1451400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>104500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>80800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>420700</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,225 +1680,232 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>49000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-33000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>13000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>38000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>255000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>82000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>59000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>17000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-71000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-255400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-186600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-175900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-149900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-332300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-164700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-172800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-159800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-153800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-168300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-177100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-169400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-180800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-188500</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2447000</v>
+      </c>
+      <c r="E21" s="3">
         <v>982000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>743000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1423000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2417000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>798000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>554000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>791000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1893000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>984000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>544000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>951000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2392000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1440000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2704800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3562200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7199000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3233800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2806800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1922400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2736400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>849700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1011900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-457800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1933100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>537500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>459200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E22" s="3">
         <v>176000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>171000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>170000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>155000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>179000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>158000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>184000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>162000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>179000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>146000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>206000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>204000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>170000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -1890,8 +1930,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
@@ -1905,180 +1945,189 @@
       <c r="AD22" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E23" s="3">
         <v>184000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>738000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>637000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1627000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>202000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>682000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>240000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>80000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>179000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>924000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>769000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1998400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2840500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6515700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2599700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2135500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1262300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2065800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>210400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>367000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1110000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1274300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-65000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-100000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>232200</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E24" s="3">
         <v>45000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>158000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>168000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>398000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>84000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-13000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>290000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>75000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-96000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>97000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>476000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>193000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>479600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>668300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1642800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>694600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>505200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>282200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>526800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>33300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-41400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-344400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>299500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-20400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-38500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>51300</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1222000</v>
+      </c>
+      <c r="E26" s="3">
         <v>139000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>580000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>469000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1229000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>118000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>25000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>392000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>165000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>176000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>82000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>448000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>576000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1518800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2172200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4872900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1905100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1630300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>980100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1538900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>177100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>408400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-765700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>974800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-61600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>180800</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="E27" s="3">
         <v>131000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>571000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>464000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1221000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>113000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>385000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>158000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>172000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>75000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>440000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>571000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1510700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2164000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4862000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1895400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1622200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>968000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1532000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>169100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>408400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-765700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>974800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-44600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-61600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>180800</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2495,20 +2556,23 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-49000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>33000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-13000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-38000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-255000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-82000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-59000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-17000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>71000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>255400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>186600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>175900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>149900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>332300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>164700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>172800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>159800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>153800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>168300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>177100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>169400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>180800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>188500</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="E33" s="3">
         <v>131000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>571000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>464000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1221000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>113000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>385000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>158000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>172000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>75000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>440000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>571000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1510700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2164000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4862000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1895400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1622200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>968000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1532000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>169100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>408400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-765700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>974800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-44600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-61600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>180800</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="E35" s="3">
         <v>131000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>571000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>464000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1221000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>113000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>385000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>158000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>172000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>75000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>440000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>571000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1510700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2164000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4862000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1895400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1622200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>968000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1532000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>169100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>408400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-765700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>974800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-44600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-61600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>180800</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>921000</v>
+      </c>
+      <c r="E41" s="3">
         <v>777000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>701000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>624000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1387000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>895000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>853000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>520000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1004000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>496000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>941000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>554000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>737000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1473000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1052800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>587300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>849800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>793700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>674000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>598100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2480600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>800400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3656200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>606500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3212500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4548700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>682300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>418100</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3309,17 +3399,17 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>171200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>542000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>112300</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
       <c r="U42" s="3">
         <v>0</v>
       </c>
@@ -3330,99 +3420,102 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>147800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>102100</v>
       </c>
-      <c r="Z42" s="3" t="s">
+      <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>393800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3557700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>178300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>310400</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8687000</v>
+      </c>
+      <c r="E43" s="3">
         <v>6284000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5675000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7687000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8086000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5612000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5390000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7786000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8123000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5561000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5398000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7713000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8595000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6009000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8414500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11788600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13763400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8854100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7247900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>463100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>478400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>496800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4628100</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>8</v>
@@ -3430,100 +3523,106 @@
       <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD43" s="3">
         <v>4543000</v>
       </c>
-      <c r="AD43" s="3" t="s">
+      <c r="AE43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>6164000</v>
+      </c>
+      <c r="E44" s="3">
         <v>8681000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6977000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5281000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5576000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7992000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6148000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4890000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5298000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8188000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6336000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5169000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6062000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9852000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>10368100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>8981000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>9688900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>12473000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8547200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6309900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6742000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8941700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>12743100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4994500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5350800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>8012200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6380900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4967500</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3533,11 +3632,11 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>284000</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
@@ -3566,394 +3665,409 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>2194000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1011300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>832200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1297100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2232700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>882900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>724500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1090700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1945100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>692600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>535200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>912000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1894400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>564300</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16167000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16475000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14749000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14474000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15615000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15362000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13792000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>13874000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15088000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15150000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14170000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14092000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15996000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18271000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22200600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22910300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>25246700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>23417900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18701800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17120700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19187700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16614200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14823800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>12888800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>14998500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17865000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>13678900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12472000</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E47" s="3">
         <v>146000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>144000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>142000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>407000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>495000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>698000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>739000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>703000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>768000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>736000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>731000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>708000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>686000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1218600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1240500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1167800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1269600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1173800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1039500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>979000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>957600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1120500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1055300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1023300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1031800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1053000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1037600</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22672000</v>
+      </c>
+      <c r="E48" s="3">
         <v>22659000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22747000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22480000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22496000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22488000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>22604000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22329000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22198000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22410000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22461000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22150000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>21920000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21832000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29570500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>28846400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27729800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27507200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>27035600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26600400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>27089900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>25904800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>50817200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>25185400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>25712800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>25742200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>26081700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>25709700</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13739000</v>
+      </c>
+      <c r="E49" s="3">
         <v>13797000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13803000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13827000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13866000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13849000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13862000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13999000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14006000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14248000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14331000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14297000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14329000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14725000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19922400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19755600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19616000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20111200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19666200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19668200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>20193000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>19522900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>37701900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>18954200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>18441700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>18179700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>18487400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>18357900</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>840000</v>
+      </c>
+      <c r="E52" s="3">
         <v>846000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>457000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>903000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>871000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>875000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>357000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>970000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>996000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>999000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>461000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>602000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>606000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>591000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1243000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1104600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>983800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>964200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>895500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>797900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>795100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>784400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1968300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>967900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>736500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>703100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>723400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53555000</v>
+      </c>
+      <c r="E54" s="3">
         <v>53923000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>52301000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>51826000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>53255000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>53069000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>51840000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>51911000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>52991000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>53575000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>52749000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>52229000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>53926000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>56592000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>74155100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>73857300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>74744000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>73270100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>67472900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>65226600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>68244500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>63783900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>60990900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59051500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>60912800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>63521900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>60024400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>58267200</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,19 +4576,20 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3">
         <v>5540000</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>8</v>
@@ -4466,11 +4597,11 @@
       <c r="H57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>5359000</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
@@ -4478,11 +4609,11 @@
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N57" s="3">
         <v>5477000</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
@@ -4490,207 +4621,213 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3">
         <v>14117500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>10726500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14276300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14683500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>12758700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8791200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>12488500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11537400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>6502100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6833800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9310000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9377700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5915400</v>
       </c>
-      <c r="AD57" s="3" t="s">
+      <c r="AE57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2327000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4164000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1732000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3374000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2783000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3839000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2927000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4344000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2947000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3694000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2654000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4659000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3267000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4864000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4060600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7921700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5052800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5332800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3229500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2135700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>716200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>700500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>545400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2444400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1879600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7284900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2170200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3856800</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9296000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9137000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2419000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6899000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8991000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8752000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2474000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6613000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9024000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9431000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2599000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6653000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9470000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10611000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1221300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1294000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1531800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>464900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>818500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>564300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>463200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>105200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14264200</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
@@ -4698,272 +4835,284 @@
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD59" s="3">
         <v>3623300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5919200</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11623000</v>
+      </c>
+      <c r="E60" s="3">
         <v>13301000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11041000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10273000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11774000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12591000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12045000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10957000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11971000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13125000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12121000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11312000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12737000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>15475000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>19399400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>19942200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>20860900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20481200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16806800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11491200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13668000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12343100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10959600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9278200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>11189600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16662600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>11708900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9776000</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10401000</v>
+      </c>
+      <c r="E61" s="3">
         <v>9782000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10287000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10806000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10855000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10868000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9880000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10412000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10423000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9944000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9912000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10328000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10359000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>10390000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12143600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10845900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10783700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11620200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11420200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>14836500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>15111500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>14537900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>14136300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>14202300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13855500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>11963500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>12071800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>11989700</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1692000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1729000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1721000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1687000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1762000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1724000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1707000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1736000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1578000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1663000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1689000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1521000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1543000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1577000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>7477200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7348100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>7086700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>7426300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7235700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>7010600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>7311700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7151800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6941500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6848100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6781800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6732000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6911900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6904200</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27617000</v>
+      </c>
+      <c r="E66" s="3">
         <v>28731000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>26936000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>26673000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>28135000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28999000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27398000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>26905000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27832000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28579000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>27548000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27033000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28468000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31287000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39081300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38202000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38790800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>39586900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35526100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>33396300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>36141000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>34088800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>32086400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>30328600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>31875300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>35406500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>30692600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28670000</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>12694000</v>
+      </c>
+      <c r="E72" s="3">
         <v>11853000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>12076000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>11839000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>11719000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10809000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11106000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11291000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11542000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11423000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11531000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11636000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11823000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11660000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16204200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>16174100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15647100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12284600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11064900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>10442300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>10114500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8618100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8537600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8448600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>9327900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8680900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9107700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9490000</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25902000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25154000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25323000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25117000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25089000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>24038000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24407000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24966000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25127000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>24953000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25156000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25145000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25413000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25261000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>35073800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>35655200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35953200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>33683200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>31946800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>31830300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>32103500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29695100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>28904500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>28722900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>29037500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>28115300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>29331800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>29597300</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="E81" s="3">
         <v>131000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>571000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>464000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1221000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>113000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>385000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>158000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>172000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>75000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>440000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>571000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1510700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2164000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4862000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1895400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1622200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>968000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1532000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>169100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>408400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-765700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>974800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-44600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-61600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>180800</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,94 +6605,98 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>614000</v>
+      </c>
+      <c r="E83" s="3">
         <v>571000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>249000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>598000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>586000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>565000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>223000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>552000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>556000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>496000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>152000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>526000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>505000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>461000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>706400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>721800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>683400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>634100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>671300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>660200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>670600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>639300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>644900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>652200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>658800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>602500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>559200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>586100</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2484000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-851000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2977000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-426000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2538000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1082000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3123000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-908000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1807000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-487000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4150000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-469000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2243000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-858000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6433900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1204800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3461500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-85300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4912500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2112800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2718400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-202400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3590300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-893500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2237700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-670000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3102600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>755500</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-469000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-299000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-685000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-498000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-398000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-279000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-709000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-475000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-491000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-324000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-660000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-580000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-732000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-422000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-974000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-636000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-378000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-450000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-568000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-474000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-522700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-432800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-641000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-347000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-379700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-462400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-706700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-664400</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-505000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-487000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-251000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-383000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-495000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-243000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-519000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-506000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-614000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-494000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-733000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-673000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-858000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-694000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1660100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-967400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-699600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-628600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-628100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-706100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-595900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-516700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-464400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-519900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-566800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-852900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1159500</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,94 +7650,98 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>266000</v>
+      </c>
+      <c r="E96" s="3">
         <v>262000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>263000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>265000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>268000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>265000</v>
       </c>
       <c r="I96" s="3">
         <v>265000</v>
       </c>
       <c r="J96" s="3">
+        <v>265000</v>
+      </c>
+      <c r="K96" s="3">
         <v>268000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>266000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>261000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>262000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>261000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>263000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>246000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-341000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-355400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-357200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-353500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-359300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-352400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-363700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-339600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-334700</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-335200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-328800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-326100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-330900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-313000</v>
       </c>
     </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1822000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1426000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2661000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>51000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1572000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1365000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2239000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>922000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-684000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>548000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3042000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>976000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2124000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2129000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4635200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-39800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2541300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>808800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4214200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1022000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-620800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-254400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2331500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>110900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4000000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>4482500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2106000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>348900</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-32000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-12000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-17000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-24000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-32000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-29000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>9000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-32600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-43900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-39200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>12400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>5400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-27000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-5500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-14600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>12900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>30600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-47100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E102" s="3">
         <v>89000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>77000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-763000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>492000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>42000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>333000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-484000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>508000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-445000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>387000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-183000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-736000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>572000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>106000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>153700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>181300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>107300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>75600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1823900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1496100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-988200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1278200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1239200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2251700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3198500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>132100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-61600</v>
       </c>
     </row>
